--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137129782</v>
       </c>
       <c r="B7" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137128711</v>
       </c>
       <c r="B8" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137128718</v>
       </c>
       <c r="B9" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>137128729</v>
       </c>
       <c r="B10" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137129782</v>
+        <v>137353423</v>
       </c>
       <c r="B7" t="n">
-        <v>87486</v>
+        <v>87593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696136</v>
+        <v>695986</v>
       </c>
       <c r="R7" t="n">
-        <v>6357088</v>
+        <v>6356842</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,53 +1355,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137129782</t>
+          <t>https://artportalen.se/Sighting/137353423</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137128711</v>
+        <v>137129782</v>
       </c>
       <c r="B8" t="n">
-        <v>87570</v>
+        <v>87486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,13 +1407,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696087</v>
+        <v>696136</v>
       </c>
       <c r="R8" t="n">
-        <v>6357087</v>
+        <v>6357088</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,19 +1461,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1487,38 +1482,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128711</t>
+          <t>https://artportalen.se/Sighting/137129782</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137128718</v>
+        <v>137353421</v>
       </c>
       <c r="B9" t="n">
-        <v>87570</v>
+        <v>87486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696141</v>
+        <v>696155</v>
       </c>
       <c r="R9" t="n">
-        <v>6356887</v>
+        <v>6356950</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,22 +1553,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,35 +1577,30 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128718</t>
+          <t>https://artportalen.se/Sighting/137353421</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137128729</v>
+        <v>137128711</v>
       </c>
       <c r="B10" t="n">
         <v>87570</v>
@@ -1645,13 +1635,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696251</v>
+        <v>696087</v>
       </c>
       <c r="R10" t="n">
-        <v>6357016</v>
+        <v>6357087</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1660,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Fröjel</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1680,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,7 +1711,354 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137128711</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137128718</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6356887</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137128718</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137128729</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696251</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6357016</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137128729</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137353420</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696143</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6356969</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137353420</t>
         </is>
       </c>
     </row>
@@ -1736,6 +2073,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137353423</v>
       </c>
       <c r="B7" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137129782</v>
       </c>
       <c r="B8" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>137353421</v>
       </c>
       <c r="B9" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137128711</v>
       </c>
       <c r="B10" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137128718</v>
       </c>
       <c r="B11" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137128729</v>
       </c>
       <c r="B12" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137353420</v>
       </c>
       <c r="B13" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137128730</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137128710</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137128715</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137128712</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137353423</v>
       </c>
       <c r="B7" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137129782</v>
       </c>
       <c r="B8" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>137353421</v>
       </c>
       <c r="B9" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137128711</v>
       </c>
       <c r="B10" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>137128718</v>
       </c>
       <c r="B11" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137128729</v>
       </c>
       <c r="B12" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137353420</v>
       </c>
       <c r="B13" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,34 +796,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137128730</v>
+        <v>137433885</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>90611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>603</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Blårödling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
+          <t>Entoloma bloxamii s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696219</v>
+        <v>696031</v>
       </c>
       <c r="R3" t="n">
-        <v>6357022</v>
+        <v>6356954</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,53 +887,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128730</t>
+          <t>https://artportalen.se/Sighting/137433885</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137128710</v>
+        <v>137128730</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696113</v>
+        <v>696219</v>
       </c>
       <c r="R4" t="n">
-        <v>6357058</v>
+        <v>6357022</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,16 +1014,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128710</t>
+          <t>https://artportalen.se/Sighting/137128730</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137128715</v>
+        <v>137433874</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>91957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696117</v>
+        <v>696153</v>
       </c>
       <c r="R5" t="n">
-        <v>6356927</v>
+        <v>6357001</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1115,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128715</t>
+          <t>https://artportalen.se/Sighting/137433874</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137128712</v>
+        <v>137128710</v>
       </c>
       <c r="B6" t="n">
-        <v>93140</v>
+        <v>91614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696066</v>
+        <v>696113</v>
       </c>
       <c r="R6" t="n">
-        <v>6357078</v>
+        <v>6357058</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,38 +1242,38 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128712</t>
+          <t>https://artportalen.se/Sighting/137128710</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137353423</v>
+        <v>137433878</v>
       </c>
       <c r="B7" t="n">
-        <v>87601</v>
+        <v>91614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248947</v>
+        <v>3286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695986</v>
+        <v>696110</v>
       </c>
       <c r="R7" t="n">
-        <v>6356842</v>
+        <v>6356958</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,49 +1343,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137353423</t>
+          <t>https://artportalen.se/Sighting/137433878</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137129782</v>
+        <v>137128715</v>
       </c>
       <c r="B8" t="n">
-        <v>87494</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696136</v>
+        <v>696117</v>
       </c>
       <c r="R8" t="n">
-        <v>6357088</v>
+        <v>6356927</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1455,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1482,38 +1470,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137129782</t>
+          <t>https://artportalen.se/Sighting/137128715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137353421</v>
+        <v>137433876</v>
       </c>
       <c r="B9" t="n">
-        <v>87494</v>
+        <v>87552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696155</v>
+        <v>696140</v>
       </c>
       <c r="R9" t="n">
-        <v>6356950</v>
+        <v>6356941</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,49 +1571,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137353421</t>
+          <t>https://artportalen.se/Sighting/137433876</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137128711</v>
+        <v>137128712</v>
       </c>
       <c r="B10" t="n">
-        <v>87578</v>
+        <v>93152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,13 +1623,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696087</v>
+        <v>696066</v>
       </c>
       <c r="R10" t="n">
-        <v>6357087</v>
+        <v>6357078</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1677,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,38 +1698,38 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128711</t>
+          <t>https://artportalen.se/Sighting/137128712</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137128718</v>
+        <v>137433873</v>
       </c>
       <c r="B11" t="n">
-        <v>87578</v>
+        <v>93152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696141</v>
+        <v>696185</v>
       </c>
       <c r="R11" t="n">
-        <v>6356887</v>
+        <v>6357021</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,22 +1769,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,60 +1793,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128718</t>
+          <t>https://artportalen.se/Sighting/137433873</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137128729</v>
+        <v>137433890</v>
       </c>
       <c r="B12" t="n">
-        <v>87578</v>
+        <v>93152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1869,13 +1851,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696251</v>
+        <v>695991</v>
       </c>
       <c r="R12" t="n">
-        <v>6357016</v>
+        <v>6356834</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,27 +1876,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Fröjel</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,60 +1905,55 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137128729</t>
+          <t>https://artportalen.se/Sighting/137433890</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137353420</v>
+        <v>137353423</v>
       </c>
       <c r="B13" t="n">
-        <v>87578</v>
+        <v>87612</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696143</v>
+        <v>695986</v>
       </c>
       <c r="R13" t="n">
-        <v>6356969</v>
+        <v>6356842</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2021,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,7 +2017,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2034,1602 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137353423</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137433875</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87612</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696135</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6356995</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433875</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137129782</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87505</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696136</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6357088</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137129782</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137353421</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87505</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696155</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6356950</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137353421</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137128711</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696087</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6357087</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137128711</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137128718</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696141</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6356887</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137128718</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137128729</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696251</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6357016</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137128729</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137353420</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696143</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6356969</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137353420</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137433877</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696133</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6356945</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433877</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137433881</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696002</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6357002</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433881</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137433882</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>695994</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6356980</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433882</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137433883</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696001</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6356969</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433883</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137433887</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696001</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6356890</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433887</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137433888</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>695993</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6356847</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433888</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137433891</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87589</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Puser, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>695991</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6356821</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Gabriella Fjordmark Lerne, Rasid Klimenta, Oskar Karl Elias Olsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433891</t>
         </is>
       </c>
     </row>
@@ -2076,6 +3647,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433885</v>
       </c>
       <c r="B3" t="n">
-        <v>90611</v>
+        <v>90612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137128730</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137433874</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137128710</v>
       </c>
       <c r="B6" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137433878</v>
       </c>
       <c r="B7" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137128715</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137433876</v>
       </c>
       <c r="B9" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137128712</v>
       </c>
       <c r="B10" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>137433873</v>
       </c>
       <c r="B11" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>137433890</v>
       </c>
       <c r="B12" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>137353423</v>
       </c>
       <c r="B13" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>137433875</v>
       </c>
       <c r="B14" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>137129782</v>
       </c>
       <c r="B15" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137353421</v>
       </c>
       <c r="B16" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137128711</v>
       </c>
       <c r="B17" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>137128718</v>
       </c>
       <c r="B18" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>137128729</v>
       </c>
       <c r="B19" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137353420</v>
       </c>
       <c r="B20" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137433877</v>
       </c>
       <c r="B21" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>137433881</v>
       </c>
       <c r="B22" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>137433882</v>
       </c>
       <c r="B23" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>137433883</v>
       </c>
       <c r="B24" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>137433887</v>
       </c>
       <c r="B25" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137433888</v>
       </c>
       <c r="B26" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>137433891</v>
       </c>
       <c r="B27" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433885</v>
       </c>
       <c r="B3" t="n">
-        <v>90612</v>
+        <v>90615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137128730</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137433874</v>
       </c>
       <c r="B5" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137128710</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137433878</v>
       </c>
       <c r="B7" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137128715</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137433876</v>
       </c>
       <c r="B9" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137128712</v>
       </c>
       <c r="B10" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>137433873</v>
       </c>
       <c r="B11" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>137433890</v>
       </c>
       <c r="B12" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>137353423</v>
       </c>
       <c r="B13" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>137433875</v>
       </c>
       <c r="B14" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>137129782</v>
       </c>
       <c r="B15" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137353421</v>
       </c>
       <c r="B16" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137128711</v>
       </c>
       <c r="B17" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>137128718</v>
       </c>
       <c r="B18" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>137128729</v>
       </c>
       <c r="B19" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137353420</v>
       </c>
       <c r="B20" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137433877</v>
       </c>
       <c r="B21" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>137433881</v>
       </c>
       <c r="B22" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>137433882</v>
       </c>
       <c r="B23" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>137433883</v>
       </c>
       <c r="B24" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>137433887</v>
       </c>
       <c r="B25" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137433888</v>
       </c>
       <c r="B26" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>137433891</v>
       </c>
       <c r="B27" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -821,6 +821,9 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Puser, Gtl</t>
@@ -875,12 +878,18 @@
           <t>15:38</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skall sekvenseras</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30892-2024 artfynd.xlsx
+++ b/artfynd/A 30892-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137128714</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433885</v>
       </c>
       <c r="B3" t="n">
-        <v>90615</v>
+        <v>90619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137128730</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137433874</v>
       </c>
       <c r="B5" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>137128710</v>
       </c>
       <c r="B6" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137433878</v>
       </c>
       <c r="B7" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>137128715</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137433876</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137128712</v>
       </c>
       <c r="B10" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>137433873</v>
       </c>
       <c r="B11" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>137433890</v>
       </c>
       <c r="B12" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>137353423</v>
       </c>
       <c r="B13" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>137433875</v>
       </c>
       <c r="B14" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137129782</v>
       </c>
       <c r="B15" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137353421</v>
       </c>
       <c r="B16" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137128711</v>
       </c>
       <c r="B17" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>137128718</v>
       </c>
       <c r="B18" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>137128729</v>
       </c>
       <c r="B19" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>137353420</v>
       </c>
       <c r="B20" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>137433877</v>
       </c>
       <c r="B21" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137433881</v>
       </c>
       <c r="B22" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137433882</v>
       </c>
       <c r="B23" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>137433883</v>
       </c>
       <c r="B24" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>137433887</v>
       </c>
       <c r="B25" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>137433888</v>
       </c>
       <c r="B26" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137433891</v>
       </c>
       <c r="B27" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
